--- a/artfynd/A 43278-2024 artfynd.xlsx
+++ b/artfynd/A 43278-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56563699</v>
+        <v>56563700</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430803.786281733</v>
+        <v>430804</v>
       </c>
       <c r="R2" t="n">
-        <v>6948343.399998426</v>
+        <v>6948343</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56563692</v>
+        <v>56563699</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431143.1122075234</v>
+        <v>430804</v>
       </c>
       <c r="R3" t="n">
-        <v>6948231.93797815</v>
+        <v>6948343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>56563698</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430844.5237259897</v>
+        <v>430845</v>
       </c>
       <c r="R4" t="n">
-        <v>6948287.831714576</v>
+        <v>6948288</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56563700</v>
+        <v>56563692</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430803.786281733</v>
+        <v>431143</v>
       </c>
       <c r="R5" t="n">
-        <v>6948343.399998426</v>
+        <v>6948232</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56563695</v>
+        <v>56563693</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431109.0432504806</v>
+        <v>431143</v>
       </c>
       <c r="R6" t="n">
-        <v>6948254.258748084</v>
+        <v>6948232</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56563693</v>
+        <v>56563695</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431143.1122075234</v>
+        <v>431109</v>
       </c>
       <c r="R7" t="n">
-        <v>6948231.93797815</v>
+        <v>6948254</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43278-2024 artfynd.xlsx
+++ b/artfynd/A 43278-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563700</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563692</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56563695</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>